--- a/resources/base_dados_padrao.xlsx
+++ b/resources/base_dados_padrao.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE DADOS" sheetId="1" r:id="Reccbfcbfab454a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASE DADOS" sheetId="1" r:id="Rd9a427ca0be64a34"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -120,9 +120,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2766,6 +2766,48 @@
         <x:v>FORNECEDOR INTERNACIONAL</x:v>
       </x:c>
     </x:row>
+    <x:row r="182">
+      <x:c r="A182" t="n">
+        <x:v>2310</x:v>
+      </x:c>
+      <x:c r="B182" t="str">
+        <x:v>DALIC</x:v>
+      </x:c>
+      <x:c r="C182" t="str">
+        <x:v>Materia prima/peças </x:v>
+      </x:c>
+      <x:c r="D182" t="str">
+        <x:v>FORNECEDOR INTERNACIONAL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" t="n">
+        <x:v>2031</x:v>
+      </x:c>
+      <x:c r="B183" t="str">
+        <x:v>NYCOTE LABORATORIES CORPORATION</x:v>
+      </x:c>
+      <x:c r="C183" t="str">
+        <x:v>Materia prima/peças </x:v>
+      </x:c>
+      <x:c r="D183" t="str">
+        <x:v>FORNECEDOR INTERNACIONAL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" t="n">
+        <x:v>2316</x:v>
+      </x:c>
+      <x:c r="B184" t="str">
+        <x:v>WWD USA GROUP LLC.</x:v>
+      </x:c>
+      <x:c r="C184" t="str">
+        <x:v>Materia prima/peças </x:v>
+      </x:c>
+      <x:c r="D184" t="str">
+        <x:v>FORNECEDOR INTERNACIONAL</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
